--- a/Data/data.xlsx
+++ b/Data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jolahn\Documents\FF1Adjacent\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2896D918-5867-4786-B286-CCFF3D251B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E21FB6F-AA8C-4D9A-B419-16D75226BDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{AC30DB01-66EC-4BC6-B3CD-409E38957771}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="404">
   <si>
     <t>Name</t>
   </si>
@@ -1228,9 +1228,6 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>MegaSceptre</t>
-  </si>
-  <si>
     <t>Crosse</t>
   </si>
   <si>
@@ -1252,13 +1249,31 @@
     <t>Compatible:</t>
   </si>
   <si>
-    <t>Rmage</t>
-  </si>
-  <si>
-    <t>Wmage</t>
-  </si>
-  <si>
-    <t>Bmage</t>
+    <t>Sceptre Pow</t>
+  </si>
+  <si>
+    <t>Mort Vivant</t>
+  </si>
+  <si>
+    <t>Mort Vivant,Démon</t>
+  </si>
+  <si>
+    <t>Achetable</t>
+  </si>
+  <si>
+    <t>Arc Bois</t>
+  </si>
+  <si>
+    <t>Arc Elfe</t>
+  </si>
+  <si>
+    <t>Arc Poison</t>
+  </si>
+  <si>
+    <t>Arc Yoichi</t>
+  </si>
+  <si>
+    <t>Efficacité: +4DMG après calcul de l'armure, +32hit (donc +1 coup), avant haste</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1347,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1351,11 +1366,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1376,6 +1400,8 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8315,13 +8341,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C074B7-7C8D-4CDA-B116-1656B1596DB3}">
-  <dimension ref="A1:U45"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
     <col min="15" max="15" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8365,28 +8392,85 @@
         <v>74</v>
       </c>
       <c r="O1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="P1" t="s">
-        <v>283</v>
+        <v>394</v>
       </c>
       <c r="Q1" t="s">
-        <v>284</v>
+        <v>7</v>
       </c>
       <c r="R1" t="s">
-        <v>285</v>
+        <v>8</v>
       </c>
       <c r="S1" t="s">
-        <v>396</v>
+        <v>9</v>
       </c>
       <c r="T1" t="s">
-        <v>397</v>
+        <v>10</v>
       </c>
       <c r="U1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="V1" t="s">
+        <v>12</v>
+      </c>
+      <c r="W1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>358</v>
       </c>
@@ -8396,14 +8480,71 @@
       <c r="C2">
         <v>10</v>
       </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
       <c r="H2">
         <v>5</v>
       </c>
       <c r="I2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>110</v>
+      </c>
+      <c r="R2" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" t="s">
+        <v>110</v>
+      </c>
+      <c r="T2" t="s">
+        <v>110</v>
+      </c>
+      <c r="U2" t="s">
+        <v>110</v>
+      </c>
+      <c r="V2" t="s">
+        <v>110</v>
+      </c>
+      <c r="W2" t="s">
+        <v>110</v>
+      </c>
+      <c r="X2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -8413,14 +8554,71 @@
       <c r="C3">
         <v>10</v>
       </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
       <c r="H3">
         <v>175</v>
       </c>
       <c r="I3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O3" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>110</v>
+      </c>
+      <c r="R3" t="s">
+        <v>110</v>
+      </c>
+      <c r="S3" t="s">
+        <v>110</v>
+      </c>
+      <c r="T3" t="s">
+        <v>110</v>
+      </c>
+      <c r="U3" t="s">
+        <v>110</v>
+      </c>
+      <c r="V3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W3" t="s">
+        <v>110</v>
+      </c>
+      <c r="X3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>359</v>
       </c>
@@ -8430,31 +8628,121 @@
       <c r="C4">
         <v>15</v>
       </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
       <c r="H4">
         <v>800</v>
       </c>
       <c r="I4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="O4" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>110</v>
+      </c>
+      <c r="R4" t="s">
+        <v>110</v>
+      </c>
+      <c r="S4" t="s">
+        <v>110</v>
+      </c>
+      <c r="T4" t="s">
+        <v>110</v>
+      </c>
+      <c r="U4" t="s">
+        <v>110</v>
+      </c>
+      <c r="V4" t="s">
+        <v>110</v>
+      </c>
+      <c r="W4" t="s">
+        <v>110</v>
+      </c>
+      <c r="X4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
         <v>360</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="20">
         <v>22</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="20">
         <v>35</v>
       </c>
-      <c r="H5">
+      <c r="G5" s="20">
+        <v>5</v>
+      </c>
+      <c r="H5" s="20">
         <v>65000</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="20" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O5" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="S5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="T5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="W5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="X5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM5" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>362</v>
       </c>
@@ -8464,11 +8752,59 @@
       <c r="C6">
         <v>5</v>
       </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
       <c r="I6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O6" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>110</v>
+      </c>
+      <c r="R6" t="s">
+        <v>110</v>
+      </c>
+      <c r="S6" t="s">
+        <v>110</v>
+      </c>
+      <c r="T6" t="s">
+        <v>110</v>
+      </c>
+      <c r="U6" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="V6" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="W6" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="X6" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>363</v>
       </c>
@@ -8478,11 +8814,59 @@
       <c r="C7">
         <v>5</v>
       </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>200</v>
+      </c>
       <c r="I7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O7" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>110</v>
+      </c>
+      <c r="R7" t="s">
+        <v>110</v>
+      </c>
+      <c r="S7" t="s">
+        <v>110</v>
+      </c>
+      <c r="T7" t="s">
+        <v>110</v>
+      </c>
+      <c r="U7" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="V7" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="W7" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="X7" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>368</v>
       </c>
@@ -8492,11 +8876,47 @@
       <c r="C8">
         <v>10</v>
       </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>550</v>
+      </c>
       <c r="I8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O8" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>110</v>
+      </c>
+      <c r="R8" t="s">
+        <v>110</v>
+      </c>
+      <c r="S8" t="s">
+        <v>110</v>
+      </c>
+      <c r="T8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>372</v>
       </c>
@@ -8506,11 +8926,47 @@
       <c r="C9">
         <v>15</v>
       </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>6000</v>
+      </c>
       <c r="I9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O9" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>110</v>
+      </c>
+      <c r="R9" t="s">
+        <v>110</v>
+      </c>
+      <c r="S9" t="s">
+        <v>110</v>
+      </c>
+      <c r="T9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>365</v>
       </c>
@@ -8520,11 +8976,59 @@
       <c r="C10">
         <v>15</v>
       </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>5000</v>
+      </c>
       <c r="I10" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O10" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>110</v>
+      </c>
+      <c r="R10" t="s">
+        <v>110</v>
+      </c>
+      <c r="S10" t="s">
+        <v>110</v>
+      </c>
+      <c r="T10" t="s">
+        <v>110</v>
+      </c>
+      <c r="U10" t="s">
+        <v>110</v>
+      </c>
+      <c r="V10" t="s">
+        <v>110</v>
+      </c>
+      <c r="W10" t="s">
+        <v>110</v>
+      </c>
+      <c r="X10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>371</v>
       </c>
@@ -8534,11 +9038,59 @@
       <c r="C11">
         <v>15</v>
       </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>8000</v>
+      </c>
       <c r="I11" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O11" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>110</v>
+      </c>
+      <c r="R11" t="s">
+        <v>110</v>
+      </c>
+      <c r="S11" t="s">
+        <v>110</v>
+      </c>
+      <c r="T11" t="s">
+        <v>110</v>
+      </c>
+      <c r="U11" t="s">
+        <v>110</v>
+      </c>
+      <c r="V11" t="s">
+        <v>110</v>
+      </c>
+      <c r="W11" t="s">
+        <v>110</v>
+      </c>
+      <c r="X11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>366</v>
       </c>
@@ -8548,11 +9100,59 @@
       <c r="C12">
         <v>15</v>
       </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>8000</v>
+      </c>
       <c r="I12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O12" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>110</v>
+      </c>
+      <c r="R12" t="s">
+        <v>110</v>
+      </c>
+      <c r="S12" t="s">
+        <v>110</v>
+      </c>
+      <c r="T12" t="s">
+        <v>110</v>
+      </c>
+      <c r="U12" t="s">
+        <v>110</v>
+      </c>
+      <c r="V12" t="s">
+        <v>110</v>
+      </c>
+      <c r="W12" t="s">
+        <v>110</v>
+      </c>
+      <c r="X12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>367</v>
       </c>
@@ -8562,11 +9162,53 @@
       <c r="C13">
         <v>10</v>
       </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>1500</v>
+      </c>
       <c r="I13" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O13" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>110</v>
+      </c>
+      <c r="R13" t="s">
+        <v>110</v>
+      </c>
+      <c r="S13" t="s">
+        <v>110</v>
+      </c>
+      <c r="T13" t="s">
+        <v>110</v>
+      </c>
+      <c r="W13" t="s">
+        <v>110</v>
+      </c>
+      <c r="X13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>369</v>
       </c>
@@ -8576,11 +9218,53 @@
       <c r="C14">
         <v>20</v>
       </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>8000</v>
+      </c>
       <c r="I14" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O14" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>110</v>
+      </c>
+      <c r="R14" t="s">
+        <v>110</v>
+      </c>
+      <c r="S14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T14" t="s">
+        <v>110</v>
+      </c>
+      <c r="W14" t="s">
+        <v>110</v>
+      </c>
+      <c r="X14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>370</v>
       </c>
@@ -8590,11 +9274,41 @@
       <c r="C15">
         <v>20</v>
       </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>60000</v>
+      </c>
       <c r="I15" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O15" t="s">
+        <v>156</v>
+      </c>
+      <c r="S15" t="s">
+        <v>110</v>
+      </c>
+      <c r="T15" t="s">
+        <v>110</v>
+      </c>
+      <c r="V15" t="s">
+        <v>110</v>
+      </c>
+      <c r="W15" t="s">
+        <v>110</v>
+      </c>
+      <c r="X15" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>378</v>
       </c>
@@ -8604,11 +9318,53 @@
       <c r="C16">
         <v>15</v>
       </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>4000</v>
+      </c>
       <c r="I16" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O16" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>110</v>
+      </c>
+      <c r="R16" t="s">
+        <v>110</v>
+      </c>
+      <c r="S16" t="s">
+        <v>110</v>
+      </c>
+      <c r="T16" t="s">
+        <v>110</v>
+      </c>
+      <c r="W16" t="s">
+        <v>110</v>
+      </c>
+      <c r="X16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>364</v>
       </c>
@@ -8618,11 +9374,47 @@
       <c r="C17">
         <v>25</v>
       </c>
+      <c r="G17">
+        <v>30</v>
+      </c>
+      <c r="H17">
+        <v>30000</v>
+      </c>
       <c r="I17" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O17" t="s">
+        <v>156</v>
+      </c>
+      <c r="R17" t="s">
+        <v>110</v>
+      </c>
+      <c r="S17" t="s">
+        <v>110</v>
+      </c>
+      <c r="T17" t="s">
+        <v>110</v>
+      </c>
+      <c r="W17" t="s">
+        <v>110</v>
+      </c>
+      <c r="X17" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>373</v>
       </c>
@@ -8632,11 +9424,62 @@
       <c r="C18">
         <v>20</v>
       </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" t="s">
+        <v>396</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
+        <v>10000</v>
+      </c>
       <c r="I18" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O18" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>110</v>
+      </c>
+      <c r="R18" t="s">
+        <v>110</v>
+      </c>
+      <c r="S18" t="s">
+        <v>110</v>
+      </c>
+      <c r="T18" t="s">
+        <v>110</v>
+      </c>
+      <c r="W18" t="s">
+        <v>110</v>
+      </c>
+      <c r="X18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>374</v>
       </c>
@@ -8646,11 +9489,59 @@
       <c r="C19">
         <v>25</v>
       </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19">
+        <v>15000</v>
+      </c>
       <c r="I19" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O19" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>110</v>
+      </c>
+      <c r="R19" t="s">
+        <v>110</v>
+      </c>
+      <c r="S19" t="s">
+        <v>110</v>
+      </c>
+      <c r="T19" t="s">
+        <v>110</v>
+      </c>
+      <c r="W19" t="s">
+        <v>110</v>
+      </c>
+      <c r="X19" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>375</v>
       </c>
@@ -8660,11 +9551,41 @@
       <c r="C20">
         <v>35</v>
       </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20">
+        <v>40000</v>
+      </c>
       <c r="I20" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O20" t="s">
+        <v>156</v>
+      </c>
+      <c r="R20" t="s">
+        <v>110</v>
+      </c>
+      <c r="S20" t="s">
+        <v>110</v>
+      </c>
+      <c r="V20" t="s">
+        <v>110</v>
+      </c>
+      <c r="W20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>376</v>
       </c>
@@ -8674,25 +9595,88 @@
       <c r="C21">
         <v>30</v>
       </c>
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" t="s">
+        <v>396</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>20000</v>
+      </c>
       <c r="I21" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="O21" t="s">
+        <v>156</v>
+      </c>
+      <c r="R21" t="s">
+        <v>110</v>
+      </c>
+      <c r="S21" t="s">
+        <v>110</v>
+      </c>
+      <c r="T21" t="s">
+        <v>110</v>
+      </c>
+      <c r="W21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="20">
         <v>45</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="20">
         <v>35</v>
       </c>
-      <c r="I22" t="s">
+      <c r="D22" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="G22" s="20">
+        <v>10</v>
+      </c>
+      <c r="H22" s="20">
+        <v>60000</v>
+      </c>
+      <c r="I22" s="20" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O22" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="R22" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>380</v>
       </c>
@@ -8702,11 +9686,62 @@
       <c r="C23">
         <v>10</v>
       </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+      <c r="H23">
+        <v>200</v>
+      </c>
       <c r="I23" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O23" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>110</v>
+      </c>
+      <c r="R23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="S23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="T23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="U23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="V23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="W23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="X23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI23" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>381</v>
       </c>
@@ -8716,11 +9751,62 @@
       <c r="C24">
         <v>10</v>
       </c>
+      <c r="G24">
+        <v>10</v>
+      </c>
+      <c r="H24">
+        <v>450</v>
+      </c>
       <c r="I24" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O24" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>110</v>
+      </c>
+      <c r="R24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="S24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="T24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="U24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="V24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="W24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="X24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -8730,25 +9816,125 @@
       <c r="C25">
         <v>35</v>
       </c>
+      <c r="G25">
+        <v>50</v>
+      </c>
+      <c r="H25">
+        <v>60000</v>
+      </c>
       <c r="I25" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="O25" t="s">
+        <v>156</v>
+      </c>
+      <c r="W25" s="21"/>
+      <c r="X25" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="20">
         <v>60</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="20">
         <v>50</v>
       </c>
-      <c r="I26" t="s">
+      <c r="G26" s="20">
+        <v>20</v>
+      </c>
+      <c r="H26" s="20">
+        <v>60000</v>
+      </c>
+      <c r="I26" s="20" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O26" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="R26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="S26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="T26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="U26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="V26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="W26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="X26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN26" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>383</v>
       </c>
@@ -8758,25 +9944,73 @@
       <c r="C27">
         <v>0</v>
       </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>10</v>
+      </c>
       <c r="I27" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>394</v>
-      </c>
-      <c r="B28">
+      <c r="O27" t="s">
+        <v>166</v>
+      </c>
+      <c r="X27" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z27" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA27" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB27" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:40" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="B28" s="20">
         <v>16</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="20">
         <v>0</v>
       </c>
-      <c r="I28" t="s">
+      <c r="G28" s="20">
+        <v>2</v>
+      </c>
+      <c r="H28" s="20">
+        <v>200</v>
+      </c>
+      <c r="I28" s="20" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O28" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="X28" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y28" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z28" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA28" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB28" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -8786,11 +10020,38 @@
       <c r="C29">
         <v>5</v>
       </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29">
+        <v>550</v>
+      </c>
       <c r="I29" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O29" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>110</v>
+      </c>
+      <c r="R29" t="s">
+        <v>110</v>
+      </c>
+      <c r="S29" t="s">
+        <v>110</v>
+      </c>
+      <c r="T29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>384</v>
       </c>
@@ -8800,11 +10061,38 @@
       <c r="C30">
         <v>5</v>
       </c>
+      <c r="G30">
+        <v>15</v>
+      </c>
+      <c r="H30">
+        <v>2000</v>
+      </c>
       <c r="I30" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O30" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>110</v>
+      </c>
+      <c r="R30" t="s">
+        <v>110</v>
+      </c>
+      <c r="S30" t="s">
+        <v>110</v>
+      </c>
+      <c r="T30" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>379</v>
       </c>
@@ -8814,25 +10102,82 @@
       <c r="C31">
         <v>10</v>
       </c>
+      <c r="G31">
+        <v>15</v>
+      </c>
+      <c r="H31">
+        <v>4500</v>
+      </c>
       <c r="I31" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>393</v>
-      </c>
-      <c r="B32">
+      <c r="O31" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>110</v>
+      </c>
+      <c r="R31" t="s">
+        <v>110</v>
+      </c>
+      <c r="S31" t="s">
+        <v>110</v>
+      </c>
+      <c r="T31" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:40" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="B32" s="20">
         <v>28</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="20">
         <v>15</v>
       </c>
-      <c r="I32" t="s">
+      <c r="G32" s="20">
+        <v>15</v>
+      </c>
+      <c r="H32" s="20">
+        <v>10000</v>
+      </c>
+      <c r="I32" s="20" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O32" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q32" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="R32" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="S32" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="T32" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="V32" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ32" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM32" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>385</v>
       </c>
@@ -8842,11 +10187,47 @@
       <c r="C33">
         <v>0</v>
       </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <v>10</v>
+      </c>
       <c r="I33" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O33" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>110</v>
+      </c>
+      <c r="R33" t="s">
+        <v>110</v>
+      </c>
+      <c r="S33" t="s">
+        <v>110</v>
+      </c>
+      <c r="T33" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM33" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>386</v>
       </c>
@@ -8856,25 +10237,91 @@
       <c r="C34">
         <v>5</v>
       </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>2500</v>
+      </c>
       <c r="I34" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="O34" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>110</v>
+      </c>
+      <c r="R34" t="s">
+        <v>110</v>
+      </c>
+      <c r="S34" t="s">
+        <v>110</v>
+      </c>
+      <c r="T34" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM34" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:40" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="20">
         <v>18</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="20">
         <v>15</v>
       </c>
-      <c r="I35" t="s">
+      <c r="G35" s="20">
+        <v>2</v>
+      </c>
+      <c r="H35" s="20">
+        <v>40000</v>
+      </c>
+      <c r="I35" s="20" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O35" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q35" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="R35" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="S35" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="T35" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="V35" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH35" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM35" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -8884,13 +10331,82 @@
       <c r="C36">
         <v>0</v>
       </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>5</v>
+      </c>
       <c r="I36" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O36" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>110</v>
+      </c>
+      <c r="R36" t="s">
+        <v>110</v>
+      </c>
+      <c r="S36" t="s">
+        <v>110</v>
+      </c>
+      <c r="T36" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B37">
         <v>12</v>
@@ -8898,13 +10414,94 @@
       <c r="C37">
         <v>0</v>
       </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>24690</v>
+      </c>
       <c r="I37" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O37" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>110</v>
+      </c>
+      <c r="R37" t="s">
+        <v>110</v>
+      </c>
+      <c r="S37" t="s">
+        <v>110</v>
+      </c>
+      <c r="T37" t="s">
+        <v>110</v>
+      </c>
+      <c r="U37" t="s">
+        <v>110</v>
+      </c>
+      <c r="V37" t="s">
+        <v>110</v>
+      </c>
+      <c r="W37" t="s">
+        <v>110</v>
+      </c>
+      <c r="X37" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B38">
         <v>14</v>
@@ -8912,13 +10509,52 @@
       <c r="C38">
         <v>0</v>
       </c>
+      <c r="F38" t="s">
+        <v>396</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>200</v>
+      </c>
       <c r="I38" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O38" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B39">
         <v>6</v>
@@ -8926,13 +10562,40 @@
       <c r="C39">
         <v>0</v>
       </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>25000</v>
+      </c>
       <c r="I39" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O39" t="s">
+        <v>156</v>
+      </c>
+      <c r="V39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B40">
         <v>12</v>
@@ -8940,46 +10603,229 @@
       <c r="C40">
         <v>10</v>
       </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>25000</v>
+      </c>
       <c r="I40" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>391</v>
-      </c>
-      <c r="B41">
+      <c r="O40" t="s">
+        <v>156</v>
+      </c>
+      <c r="V40" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM40" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:40" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="B41" s="20">
         <v>15</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="20">
         <v>15</v>
       </c>
-      <c r="I41" t="s">
+      <c r="G41" s="20">
+        <v>0</v>
+      </c>
+      <c r="H41" s="20">
+        <v>50000</v>
+      </c>
+      <c r="I41" s="20" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O41" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="V41" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL41" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM41" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN41" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>399</v>
+      </c>
+      <c r="B42">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="G42">
+        <v>20</v>
+      </c>
+      <c r="H42">
+        <v>10</v>
+      </c>
       <c r="I42" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O42" t="s">
+        <v>166</v>
+      </c>
+      <c r="S42" t="s">
+        <v>110</v>
+      </c>
+      <c r="U42" t="s">
+        <v>110</v>
+      </c>
+      <c r="V42" t="s">
+        <v>110</v>
+      </c>
+      <c r="W42" t="s">
+        <v>110</v>
+      </c>
+      <c r="X42" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>400</v>
+      </c>
+      <c r="B43">
+        <v>18</v>
+      </c>
+      <c r="C43">
+        <v>15</v>
+      </c>
+      <c r="G43">
+        <v>20</v>
+      </c>
+      <c r="H43">
+        <v>3500</v>
+      </c>
       <c r="I43" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O43" t="s">
+        <v>166</v>
+      </c>
+      <c r="S43" t="s">
+        <v>110</v>
+      </c>
+      <c r="U43" t="s">
+        <v>110</v>
+      </c>
+      <c r="V43" t="s">
+        <v>110</v>
+      </c>
+      <c r="W43" t="s">
+        <v>110</v>
+      </c>
+      <c r="X43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>401</v>
+      </c>
+      <c r="B44">
+        <v>22</v>
+      </c>
+      <c r="C44">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
+        <v>39</v>
+      </c>
+      <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44">
+        <v>20</v>
+      </c>
+      <c r="H44">
+        <v>8000</v>
+      </c>
       <c r="I44" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O44" t="s">
+        <v>156</v>
+      </c>
+      <c r="S44" t="s">
+        <v>110</v>
+      </c>
+      <c r="U44" t="s">
+        <v>110</v>
+      </c>
+      <c r="V44" t="s">
+        <v>110</v>
+      </c>
+      <c r="W44" t="s">
+        <v>110</v>
+      </c>
+      <c r="X44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>402</v>
+      </c>
+      <c r="B45">
+        <v>35</v>
+      </c>
+      <c r="C45">
+        <v>30</v>
+      </c>
+      <c r="G45">
+        <v>30</v>
+      </c>
+      <c r="H45">
+        <v>40000</v>
+      </c>
       <c r="I45" t="s">
         <v>357</v>
       </c>
+      <c r="O45" t="s">
+        <v>156</v>
+      </c>
+      <c r="S45" t="s">
+        <v>110</v>
+      </c>
+      <c r="W45" t="s">
+        <v>110</v>
+      </c>
+      <c r="X45" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N50" t="s">
+        <v>403</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Data/data.xlsx
+++ b/Data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jolahn\Documents\FF1Adjacent\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E21FB6F-AA8C-4D9A-B419-16D75226BDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92514D4F-3C2F-4B22-93BE-3D0E3ECF330A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{AC30DB01-66EC-4BC6-B3CD-409E38957771}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21000" xr2:uid="{AC30DB01-66EC-4BC6-B3CD-409E38957771}"/>
   </bookViews>
   <sheets>
     <sheet name="Armure" sheetId="2" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="445">
   <si>
     <t>Name</t>
   </si>
@@ -1243,9 +1243,6 @@
     <t>Hache Lux</t>
   </si>
   <si>
-    <t>Barre de fer</t>
-  </si>
-  <si>
     <t>Compatible:</t>
   </si>
   <si>
@@ -1274,6 +1271,132 @@
   </si>
   <si>
     <t>Efficacité: +4DMG après calcul de l'armure, +32hit (donc +1 coup), avant haste</t>
+  </si>
+  <si>
+    <t>Casque</t>
+  </si>
+  <si>
+    <t>Gants</t>
+  </si>
+  <si>
+    <t>Tonfa</t>
+  </si>
+  <si>
+    <t>Targe</t>
+  </si>
+  <si>
+    <t>Pavois de Cuir</t>
+  </si>
+  <si>
+    <t>Bouclier d'acier</t>
+  </si>
+  <si>
+    <t>Gants d'acier</t>
+  </si>
+  <si>
+    <t>Écu de mythril</t>
+  </si>
+  <si>
+    <t>Aegis</t>
+  </si>
+  <si>
+    <t>Égide Adamante</t>
+  </si>
+  <si>
+    <t>Bouclier Glacial</t>
+  </si>
+  <si>
+    <t>Bouclier Igné</t>
+  </si>
+  <si>
+    <t>Cape Protectrice</t>
+  </si>
+  <si>
+    <t>Casque de Cuir</t>
+  </si>
+  <si>
+    <t>Ruban</t>
+  </si>
+  <si>
+    <t>Heaume</t>
+  </si>
+  <si>
+    <t>Heaume de Mythril</t>
+  </si>
+  <si>
+    <t>Casque Curatif</t>
+  </si>
+  <si>
+    <t>Heaume de Diamant</t>
+  </si>
+  <si>
+    <t>Robe</t>
+  </si>
+  <si>
+    <t>Robe Blanche</t>
+  </si>
+  <si>
+    <t>Robe Noire</t>
+  </si>
+  <si>
+    <t>Cuirasse</t>
+  </si>
+  <si>
+    <t>Cotte de Maille</t>
+  </si>
+  <si>
+    <t>Armure d'acier</t>
+  </si>
+  <si>
+    <t>Cotte de Mythril</t>
+  </si>
+  <si>
+    <t>Armure de Fer</t>
+  </si>
+  <si>
+    <t>Cotte de Feu</t>
+  </si>
+  <si>
+    <t>Armure de Diamant</t>
+  </si>
+  <si>
+    <t>Armure glacée</t>
+  </si>
+  <si>
+    <t>Armure Draconique</t>
+  </si>
+  <si>
+    <t>Brassard de Cuivre</t>
+  </si>
+  <si>
+    <t>Brassard Argenté</t>
+  </si>
+  <si>
+    <t>Brassard Doré</t>
+  </si>
+  <si>
+    <t>Brassard de Diamant</t>
+  </si>
+  <si>
+    <t>Gants de Cuir</t>
+  </si>
+  <si>
+    <t>Gant de Cuivre</t>
+  </si>
+  <si>
+    <t>Gants de Mythril</t>
+  </si>
+  <si>
+    <t>Gants de Diamant</t>
+  </si>
+  <si>
+    <t>Gigagants</t>
+  </si>
+  <si>
+    <t>Foudroyeurs</t>
+  </si>
+  <si>
+    <t>Anneau Protecteur</t>
   </si>
 </sst>
 </file>
@@ -2521,8 +2644,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C52F2B5-65CB-474E-8DCF-13CF0882A92B}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2563,6 +2690,377 @@
       </c>
       <c r="M1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>407</v>
+      </c>
+      <c r="G2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>406</v>
+      </c>
+      <c r="G3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>408</v>
+      </c>
+      <c r="G4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>410</v>
+      </c>
+      <c r="G5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>413</v>
+      </c>
+      <c r="G7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>412</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>411</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>415</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>416</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>417</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>403</v>
+      </c>
+      <c r="G13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>418</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>419</v>
+      </c>
+      <c r="G15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>420</v>
+      </c>
+      <c r="G16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>421</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>422</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>423</v>
+      </c>
+      <c r="G19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>424</v>
+      </c>
+      <c r="G20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>425</v>
+      </c>
+      <c r="G21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>426</v>
+      </c>
+      <c r="G22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>428</v>
+      </c>
+      <c r="G23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>429</v>
+      </c>
+      <c r="G24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>427</v>
+      </c>
+      <c r="G25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>430</v>
+      </c>
+      <c r="G26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>432</v>
+      </c>
+      <c r="G27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>431</v>
+      </c>
+      <c r="G28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>433</v>
+      </c>
+      <c r="G29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>434</v>
+      </c>
+      <c r="G30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>435</v>
+      </c>
+      <c r="G31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>436</v>
+      </c>
+      <c r="G32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>437</v>
+      </c>
+      <c r="G33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>438</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>-1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>439</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>-3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>409</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36">
+        <v>-5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>440</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>-3</v>
+      </c>
+      <c r="G37" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>443</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>-3</v>
+      </c>
+      <c r="G38" t="s">
+        <v>404</v>
+      </c>
+      <c r="H38" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>442</v>
+      </c>
+      <c r="B39">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>-3</v>
+      </c>
+      <c r="G39" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>441</v>
+      </c>
+      <c r="B40">
+        <v>8</v>
+      </c>
+      <c r="C40">
+        <v>-3</v>
+      </c>
+      <c r="G40" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>444</v>
+      </c>
+      <c r="B41">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>-1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -8392,10 +8890,10 @@
         <v>74</v>
       </c>
       <c r="O1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q1" t="s">
         <v>7</v>
@@ -9428,7 +9926,7 @@
         <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G18">
         <v>10</v>
@@ -9599,7 +10097,7 @@
         <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -9658,7 +10156,7 @@
         <v>142</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G22" s="20">
         <v>10</v>
@@ -9974,7 +10472,7 @@
     </row>
     <row r="28" spans="1:40" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="B28" s="20">
         <v>16</v>
@@ -10406,7 +10904,7 @@
     </row>
     <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B37">
         <v>12</v>
@@ -10510,7 +11008,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -10668,7 +11166,7 @@
     </row>
     <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B42">
         <v>6</v>
@@ -10706,7 +11204,7 @@
     </row>
     <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B43">
         <v>18</v>
@@ -10744,7 +11242,7 @@
     </row>
     <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B44">
         <v>22</v>
@@ -10788,7 +11286,7 @@
     </row>
     <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B45">
         <v>35</v>
@@ -10820,7 +11318,7 @@
     </row>
     <row r="50" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N50" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
